--- a/static/data/exports/Retro_MN_AE_2017.xlsx
+++ b/static/data/exports/Retro_MN_AE_2017.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -576,6 +576,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>49</v>
+      </c>
       <c r="Q2" t="b">
         <v>1</v>
       </c>
@@ -638,6 +651,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>59</v>
+      </c>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
@@ -700,6 +726,19 @@
           <t>CPM</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>56</v>
+      </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
@@ -824,6 +863,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>78</v>
+      </c>
       <c r="Q6" t="b">
         <v>0</v>
       </c>
@@ -886,6 +938,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>56</v>
+      </c>
       <c r="Q7" t="b">
         <v>0</v>
       </c>
@@ -948,6 +1013,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>52</v>
+      </c>
       <c r="Q8" t="b">
         <v>0</v>
       </c>
@@ -1010,6 +1088,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>36</v>
+      </c>
       <c r="Q9" t="b">
         <v>0</v>
       </c>
@@ -1134,6 +1225,19 @@
           <t>MDPF</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>66</v>
+      </c>
       <c r="Q11" t="b">
         <v>0</v>
       </c>
@@ -1196,6 +1300,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>45</v>
+      </c>
       <c r="Q12" t="b">
         <v>0</v>
       </c>
@@ -1258,6 +1375,19 @@
           <t>MPEP</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>58</v>
+      </c>
       <c r="Q13" t="b">
         <v>0</v>
       </c>
@@ -1320,6 +1450,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>33</v>
+      </c>
       <c r="Q14" t="b">
         <v>0</v>
       </c>
@@ -1382,6 +1525,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>71</v>
+      </c>
       <c r="Q15" t="b">
         <v>0</v>
       </c>
@@ -1444,6 +1600,19 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>54</v>
+      </c>
       <c r="Q16" t="b">
         <v>0</v>
       </c>
@@ -1568,6 +1737,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>44</v>
+      </c>
       <c r="Q18" t="b">
         <v>0</v>
       </c>
@@ -1630,6 +1812,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>37</v>
+      </c>
       <c r="Q19" t="b">
         <v>1</v>
       </c>
@@ -1692,6 +1887,19 @@
           <t>MNDF</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>60</v>
+      </c>
       <c r="Q20" t="b">
         <v>0</v>
       </c>
@@ -1754,6 +1962,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>42</v>
+      </c>
       <c r="Q21" t="b">
         <v>0</v>
       </c>
@@ -1878,6 +2099,19 @@
           <t>MPEP</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>65</v>
+      </c>
       <c r="Q23" t="b">
         <v>0</v>
       </c>
@@ -1940,6 +2174,19 @@
           <t>AIFB</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>48</v>
+      </c>
       <c r="Q24" t="b">
         <v>0</v>
       </c>
@@ -2002,6 +2249,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>48</v>
+      </c>
       <c r="Q25" t="b">
         <v>0</v>
       </c>
@@ -2064,6 +2324,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>41</v>
+      </c>
       <c r="Q26" t="b">
         <v>0</v>
       </c>
@@ -2126,6 +2399,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>53</v>
+      </c>
       <c r="Q27" t="b">
         <v>0</v>
       </c>
@@ -2250,6 +2536,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>31</v>
+      </c>
       <c r="Q29" t="b">
         <v>0</v>
       </c>
@@ -2312,6 +2611,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>37</v>
+      </c>
       <c r="Q30" t="b">
         <v>0</v>
       </c>
@@ -2374,6 +2686,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>35</v>
+      </c>
       <c r="Q31" t="b">
         <v>0</v>
       </c>
@@ -2436,6 +2761,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>43</v>
+      </c>
       <c r="Q32" t="b">
         <v>0</v>
       </c>
@@ -2498,6 +2836,19 @@
           <t>NEINDP</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>41</v>
+      </c>
       <c r="Q33" t="b">
         <v>0</v>
       </c>
@@ -2560,6 +2911,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>53</v>
+      </c>
       <c r="Q34" t="b">
         <v>0</v>
       </c>
@@ -2622,6 +2986,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>37</v>
+      </c>
       <c r="Q35" t="b">
         <v>0</v>
       </c>
@@ -2684,6 +3061,19 @@
           <t>MNDF</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>45</v>
+      </c>
       <c r="Q36" t="b">
         <v>0</v>
       </c>
@@ -2746,6 +3136,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>47</v>
+      </c>
       <c r="Q37" t="b">
         <v>0</v>
       </c>
@@ -2870,6 +3273,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>46</v>
+      </c>
       <c r="Q39" t="b">
         <v>0</v>
       </c>
@@ -2932,6 +3348,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>69</v>
+      </c>
       <c r="Q40" t="b">
         <v>0</v>
       </c>
@@ -2994,6 +3423,19 @@
           <t>MNDF</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>54</v>
+      </c>
       <c r="Q41" t="b">
         <v>0</v>
       </c>
@@ -3118,6 +3560,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>55</v>
+      </c>
       <c r="Q43" t="b">
         <v>0</v>
       </c>
@@ -3180,6 +3635,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>58</v>
+      </c>
       <c r="Q44" t="b">
         <v>0</v>
       </c>
@@ -3242,6 +3710,19 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>46</v>
+      </c>
       <c r="Q45" t="b">
         <v>0</v>
       </c>
@@ -3366,6 +3847,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>52</v>
+      </c>
       <c r="Q47" t="b">
         <v>0</v>
       </c>
@@ -3428,6 +3922,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>52</v>
+      </c>
       <c r="Q48" t="b">
         <v>0</v>
       </c>
@@ -3490,6 +3997,19 @@
           <t>PRJA</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>33</v>
+      </c>
       <c r="Q49" t="b">
         <v>0</v>
       </c>
@@ -3614,6 +4134,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>63</v>
+      </c>
       <c r="Q51" t="b">
         <v>0</v>
       </c>
@@ -3676,6 +4209,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>79</v>
+      </c>
       <c r="Q52" t="b">
         <v>0</v>
       </c>
@@ -3738,6 +4284,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>59</v>
+      </c>
       <c r="Q53" t="b">
         <v>0</v>
       </c>
@@ -3800,6 +4359,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>35</v>
+      </c>
       <c r="Q54" t="b">
         <v>0</v>
       </c>
@@ -3924,6 +4496,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>39</v>
+      </c>
       <c r="Q56" t="b">
         <v>0</v>
       </c>
@@ -3986,6 +4571,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>53</v>
+      </c>
       <c r="Q57" t="b">
         <v>0</v>
       </c>
@@ -4048,6 +4646,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>62</v>
+      </c>
       <c r="Q58" t="b">
         <v>0</v>
       </c>
@@ -4172,8 +4783,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>53</v>
+      </c>
       <c r="Q60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
         <v>29</v>
@@ -4234,6 +4858,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>55</v>
+      </c>
       <c r="Q61" t="b">
         <v>0</v>
       </c>
@@ -4296,6 +4933,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>68</v>
+      </c>
       <c r="Q62" t="b">
         <v>0</v>
       </c>
@@ -4358,6 +5008,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>51</v>
+      </c>
       <c r="Q63" t="b">
         <v>0</v>
       </c>
@@ -4420,6 +5083,19 @@
           <t>NEINDP</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>61</v>
+      </c>
       <c r="Q64" t="b">
         <v>0</v>
       </c>
@@ -4544,6 +5220,19 @@
           <t>MPEP</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>33</v>
+      </c>
       <c r="Q66" t="b">
         <v>0</v>
       </c>
@@ -4606,6 +5295,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>52</v>
+      </c>
       <c r="Q67" t="b">
         <v>0</v>
       </c>
@@ -4668,6 +5370,19 @@
           <t>MNDF</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>47</v>
+      </c>
       <c r="Q68" t="b">
         <v>0</v>
       </c>
@@ -4730,6 +5445,19 @@
           <t>AIFB</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>52</v>
+      </c>
       <c r="Q69" t="b">
         <v>0</v>
       </c>
@@ -4792,6 +5520,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>54</v>
+      </c>
       <c r="Q70" t="b">
         <v>0</v>
       </c>
@@ -4854,6 +5595,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>51</v>
+      </c>
       <c r="Q71" t="b">
         <v>1</v>
       </c>
@@ -4978,6 +5732,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>60</v>
+      </c>
       <c r="Q73" t="b">
         <v>0</v>
       </c>
@@ -5040,6 +5807,19 @@
           <t>MPEP</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>35</v>
+      </c>
       <c r="Q74" t="b">
         <v>0</v>
       </c>
@@ -5102,6 +5882,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>43</v>
+      </c>
       <c r="Q75" t="b">
         <v>0</v>
       </c>
@@ -5164,6 +5957,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>49</v>
+      </c>
       <c r="Q76" t="b">
         <v>1</v>
       </c>
@@ -5226,6 +6032,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>43</v>
+      </c>
       <c r="Q77" t="b">
         <v>0</v>
       </c>
@@ -5288,6 +6107,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>41</v>
+      </c>
       <c r="Q78" t="b">
         <v>0</v>
       </c>
@@ -5412,6 +6244,19 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>57</v>
+      </c>
       <c r="Q80" t="b">
         <v>0</v>
       </c>
@@ -5474,6 +6319,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>32</v>
+      </c>
       <c r="Q81" t="b">
         <v>0</v>
       </c>
@@ -5536,6 +6394,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>77</v>
+      </c>
       <c r="Q82" t="b">
         <v>0</v>
       </c>
@@ -5660,6 +6531,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>42</v>
+      </c>
       <c r="Q84" t="b">
         <v>0</v>
       </c>
@@ -5722,6 +6606,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>38</v>
+      </c>
       <c r="Q85" t="b">
         <v>0</v>
       </c>
@@ -5784,6 +6681,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>54</v>
+      </c>
       <c r="Q86" t="b">
         <v>1</v>
       </c>
@@ -5908,6 +6818,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>52</v>
+      </c>
       <c r="Q88" t="b">
         <v>0</v>
       </c>
@@ -5970,6 +6893,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>68</v>
+      </c>
       <c r="Q89" t="b">
         <v>1</v>
       </c>
@@ -6032,6 +6968,19 @@
           <t>NEINDP</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>65</v>
+      </c>
       <c r="Q90" t="b">
         <v>0</v>
       </c>
@@ -6156,6 +7105,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>45</v>
+      </c>
       <c r="Q92" t="b">
         <v>0</v>
       </c>
@@ -6218,6 +7180,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>52</v>
+      </c>
       <c r="Q93" t="b">
         <v>0</v>
       </c>
@@ -6342,6 +7317,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>35</v>
+      </c>
       <c r="Q95" t="b">
         <v>0</v>
       </c>
@@ -6404,6 +7392,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>52</v>
+      </c>
       <c r="Q96" t="b">
         <v>0</v>
       </c>
@@ -6466,6 +7467,19 @@
           <t>NEINDP</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>58</v>
+      </c>
       <c r="Q97" t="b">
         <v>0</v>
       </c>
@@ -6528,6 +7542,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>49</v>
+      </c>
       <c r="Q98" t="b">
         <v>0</v>
       </c>
@@ -6590,6 +7617,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>48</v>
+      </c>
       <c r="Q99" t="b">
         <v>0</v>
       </c>
@@ -6714,6 +7754,19 @@
           <t>CPM</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>54</v>
+      </c>
       <c r="Q101" t="b">
         <v>0</v>
       </c>
@@ -6776,6 +7829,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>54</v>
+      </c>
       <c r="Q102" t="b">
         <v>1</v>
       </c>
@@ -6838,6 +7904,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>75</v>
+      </c>
       <c r="Q103" t="b">
         <v>0</v>
       </c>
@@ -6900,6 +7979,19 @@
           <t>NEINDP</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>46</v>
+      </c>
       <c r="Q104" t="b">
         <v>0</v>
       </c>
@@ -6962,6 +8054,19 @@
           <t>MNDF</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>40</v>
+      </c>
       <c r="Q105" t="b">
         <v>0</v>
       </c>
@@ -7024,8 +8129,21 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>63</v>
+      </c>
       <c r="Q106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
         <v>29</v>
@@ -7086,6 +8204,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>46</v>
+      </c>
       <c r="Q107" t="b">
         <v>0</v>
       </c>
@@ -7210,6 +8341,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>50</v>
+      </c>
       <c r="Q109" t="b">
         <v>0</v>
       </c>
@@ -7272,6 +8416,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>57</v>
+      </c>
       <c r="Q110" t="b">
         <v>1</v>
       </c>
@@ -7334,6 +8491,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>48</v>
+      </c>
       <c r="Q111" t="b">
         <v>0</v>
       </c>
@@ -7396,6 +8566,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>61</v>
+      </c>
       <c r="Q112" t="b">
         <v>0</v>
       </c>
@@ -7458,6 +8641,19 @@
           <t>NEINDP</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>50</v>
+      </c>
       <c r="Q113" t="b">
         <v>0</v>
       </c>
@@ -7582,6 +8778,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>58</v>
+      </c>
       <c r="Q115" t="b">
         <v>0</v>
       </c>
@@ -7644,6 +8853,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>42</v>
+      </c>
       <c r="Q116" t="b">
         <v>0</v>
       </c>
@@ -7706,6 +8928,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>46</v>
+      </c>
       <c r="Q117" t="b">
         <v>0</v>
       </c>
@@ -7768,6 +9003,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>43</v>
+      </c>
       <c r="Q118" t="b">
         <v>0</v>
       </c>
@@ -7830,6 +9078,19 @@
           <t>MNDF</t>
         </is>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>59</v>
+      </c>
       <c r="Q119" t="b">
         <v>0</v>
       </c>
@@ -7892,6 +9153,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>56</v>
+      </c>
       <c r="Q120" t="b">
         <v>0</v>
       </c>
@@ -8016,6 +9290,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>29</v>
+      </c>
       <c r="Q122" t="b">
         <v>0</v>
       </c>
@@ -8078,8 +9365,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>53</v>
+      </c>
       <c r="Q123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R123" t="n">
         <v>29</v>
@@ -8202,8 +9502,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>47</v>
+      </c>
       <c r="Q125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R125" t="n">
         <v>29</v>
@@ -8264,6 +9577,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>78</v>
+      </c>
       <c r="Q126" t="b">
         <v>0</v>
       </c>
@@ -8388,6 +9714,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>60</v>
+      </c>
       <c r="Q128" t="b">
         <v>0</v>
       </c>
@@ -8450,6 +9789,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>63</v>
+      </c>
       <c r="Q129" t="b">
         <v>0</v>
       </c>
@@ -8512,6 +9864,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>50</v>
+      </c>
       <c r="Q130" t="b">
         <v>0</v>
       </c>
@@ -8574,6 +9939,19 @@
           <t>MNDF</t>
         </is>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>59</v>
+      </c>
       <c r="Q131" t="b">
         <v>0</v>
       </c>
@@ -8698,6 +10076,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
+        <v>53</v>
+      </c>
       <c r="Q133" t="b">
         <v>1</v>
       </c>
@@ -8760,6 +10151,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>50</v>
+      </c>
       <c r="Q134" t="b">
         <v>0</v>
       </c>
@@ -8822,6 +10226,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>52</v>
+      </c>
       <c r="Q135" t="b">
         <v>0</v>
       </c>
@@ -8946,6 +10363,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>56</v>
+      </c>
       <c r="Q137" t="b">
         <v>0</v>
       </c>
@@ -9008,6 +10438,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>66</v>
+      </c>
       <c r="Q138" t="b">
         <v>0</v>
       </c>
@@ -9070,6 +10513,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>36</v>
+      </c>
       <c r="Q139" t="b">
         <v>1</v>
       </c>
@@ -9132,6 +10588,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
+        <v>52</v>
+      </c>
       <c r="Q140" t="b">
         <v>0</v>
       </c>
@@ -9256,8 +10725,21 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>45</v>
+      </c>
       <c r="Q142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
         <v>29</v>
@@ -9318,6 +10800,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>46</v>
+      </c>
       <c r="Q143" t="b">
         <v>0</v>
       </c>
@@ -9380,6 +10875,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>66</v>
+      </c>
       <c r="Q144" t="b">
         <v>0</v>
       </c>
@@ -9442,6 +10950,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>63</v>
+      </c>
       <c r="Q145" t="b">
         <v>0</v>
       </c>
@@ -9566,6 +11087,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>70</v>
+      </c>
       <c r="Q147" t="b">
         <v>1</v>
       </c>
@@ -9628,6 +11162,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>66</v>
+      </c>
       <c r="Q148" t="b">
         <v>0</v>
       </c>
@@ -9690,6 +11237,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>57</v>
+      </c>
       <c r="Q149" t="b">
         <v>0</v>
       </c>
@@ -9752,6 +11312,19 @@
           <t>MNDF</t>
         </is>
       </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>36</v>
+      </c>
       <c r="Q150" t="b">
         <v>0</v>
       </c>
@@ -9876,6 +11449,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>39</v>
+      </c>
       <c r="Q152" t="b">
         <v>0</v>
       </c>
@@ -9938,6 +11524,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>29</v>
+      </c>
       <c r="Q153" t="b">
         <v>0</v>
       </c>
@@ -10000,6 +11599,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>53</v>
+      </c>
       <c r="Q154" t="b">
         <v>0</v>
       </c>
@@ -10062,6 +11674,19 @@
           <t>NEINDP</t>
         </is>
       </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>59</v>
+      </c>
       <c r="Q155" t="b">
         <v>0</v>
       </c>
@@ -10186,6 +11811,19 @@
           <t>MNDF</t>
         </is>
       </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>59</v>
+      </c>
       <c r="Q157" t="b">
         <v>0</v>
       </c>
@@ -10248,6 +11886,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P158" t="n">
+        <v>60</v>
+      </c>
       <c r="Q158" t="b">
         <v>0</v>
       </c>
@@ -10310,6 +11961,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
+        <v>68</v>
+      </c>
       <c r="Q159" t="b">
         <v>1</v>
       </c>
@@ -10372,6 +12036,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P160" t="n">
+        <v>48</v>
+      </c>
       <c r="Q160" t="b">
         <v>0</v>
       </c>
@@ -10434,6 +12111,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P161" t="n">
+        <v>43</v>
+      </c>
       <c r="Q161" t="b">
         <v>0</v>
       </c>
@@ -10558,6 +12248,19 @@
           <t>PRJA</t>
         </is>
       </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>44</v>
+      </c>
       <c r="Q163" t="b">
         <v>0</v>
       </c>
@@ -10620,6 +12323,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P164" t="n">
+        <v>66</v>
+      </c>
       <c r="Q164" t="b">
         <v>0</v>
       </c>
@@ -10682,6 +12398,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P165" t="n">
+        <v>44</v>
+      </c>
       <c r="Q165" t="b">
         <v>1</v>
       </c>
@@ -10744,6 +12473,19 @@
           <t>NEINDP</t>
         </is>
       </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P166" t="n">
+        <v>42</v>
+      </c>
       <c r="Q166" t="b">
         <v>0</v>
       </c>
@@ -10806,6 +12548,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P167" t="n">
+        <v>53</v>
+      </c>
       <c r="Q167" t="b">
         <v>0</v>
       </c>
@@ -10868,6 +12623,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P168" t="n">
+        <v>47</v>
+      </c>
       <c r="Q168" t="b">
         <v>0</v>
       </c>
@@ -10992,6 +12760,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P170" t="n">
+        <v>27</v>
+      </c>
       <c r="Q170" t="b">
         <v>0</v>
       </c>
@@ -11054,6 +12835,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P171" t="n">
+        <v>53</v>
+      </c>
       <c r="Q171" t="b">
         <v>0</v>
       </c>
@@ -11116,6 +12910,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P172" t="n">
+        <v>48</v>
+      </c>
       <c r="Q172" t="b">
         <v>1</v>
       </c>
@@ -11178,6 +12985,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P173" t="n">
+        <v>46</v>
+      </c>
       <c r="Q173" t="b">
         <v>0</v>
       </c>
@@ -11302,6 +13122,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P175" t="n">
+        <v>45</v>
+      </c>
       <c r="Q175" t="b">
         <v>0</v>
       </c>
@@ -11364,6 +13197,19 @@
           <t>MPEP</t>
         </is>
       </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P176" t="n">
+        <v>45</v>
+      </c>
       <c r="Q176" t="b">
         <v>0</v>
       </c>
@@ -11426,6 +13272,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P177" t="n">
+        <v>51</v>
+      </c>
       <c r="Q177" t="b">
         <v>0</v>
       </c>
@@ -11488,6 +13347,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P178" t="n">
+        <v>57</v>
+      </c>
       <c r="Q178" t="b">
         <v>0</v>
       </c>
@@ -11550,6 +13422,19 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P179" t="n">
+        <v>51</v>
+      </c>
       <c r="Q179" t="b">
         <v>0</v>
       </c>
@@ -11612,6 +13497,19 @@
           <t>MNDF</t>
         </is>
       </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P180" t="n">
+        <v>58</v>
+      </c>
       <c r="Q180" t="b">
         <v>0</v>
       </c>
@@ -11736,6 +13634,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P182" t="n">
+        <v>29</v>
+      </c>
       <c r="Q182" t="b">
         <v>0</v>
       </c>
@@ -11798,6 +13709,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P183" t="n">
+        <v>53</v>
+      </c>
       <c r="Q183" t="b">
         <v>0</v>
       </c>
@@ -11922,6 +13846,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P185" t="n">
+        <v>67</v>
+      </c>
       <c r="Q185" t="b">
         <v>0</v>
       </c>
@@ -11984,6 +13921,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P186" t="n">
+        <v>48</v>
+      </c>
       <c r="Q186" t="b">
         <v>1</v>
       </c>
@@ -12046,6 +13996,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P187" t="n">
+        <v>48</v>
+      </c>
       <c r="Q187" t="b">
         <v>0</v>
       </c>
@@ -12108,6 +14071,19 @@
           <t>NEINDP</t>
         </is>
       </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P188" t="n">
+        <v>43</v>
+      </c>
       <c r="Q188" t="b">
         <v>0</v>
       </c>
@@ -12170,6 +14146,19 @@
           <t>MNDF</t>
         </is>
       </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P189" t="n">
+        <v>41</v>
+      </c>
       <c r="Q189" t="b">
         <v>0</v>
       </c>
@@ -12232,6 +14221,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P190" t="n">
+        <v>46</v>
+      </c>
       <c r="Q190" t="b">
         <v>0</v>
       </c>
@@ -12356,6 +14358,19 @@
           <t>PRJA</t>
         </is>
       </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P192" t="n">
+        <v>44</v>
+      </c>
       <c r="Q192" t="b">
         <v>0</v>
       </c>
@@ -12418,6 +14433,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P193" t="n">
+        <v>65</v>
+      </c>
       <c r="Q193" t="b">
         <v>1</v>
       </c>
@@ -12480,6 +14508,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P194" t="n">
+        <v>48</v>
+      </c>
       <c r="Q194" t="b">
         <v>0</v>
       </c>
@@ -12542,8 +14583,21 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P195" t="n">
+        <v>63</v>
+      </c>
       <c r="Q195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R195" t="n">
         <v>29</v>
@@ -12666,6 +14720,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P197" t="n">
+        <v>62</v>
+      </c>
       <c r="Q197" t="b">
         <v>0</v>
       </c>
@@ -12728,8 +14795,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P198" t="n">
+        <v>58</v>
+      </c>
       <c r="Q198" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
         <v>29</v>
@@ -12852,6 +14932,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P200" t="n">
+        <v>55</v>
+      </c>
       <c r="Q200" t="b">
         <v>1</v>
       </c>
@@ -12914,6 +15007,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P201" t="n">
+        <v>36</v>
+      </c>
       <c r="Q201" t="b">
         <v>0</v>
       </c>
@@ -13038,6 +15144,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P203" t="n">
+        <v>51</v>
+      </c>
       <c r="Q203" t="b">
         <v>0</v>
       </c>
@@ -13100,6 +15219,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P204" t="n">
+        <v>74</v>
+      </c>
       <c r="Q204" t="b">
         <v>1</v>
       </c>
@@ -13162,6 +15294,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P205" t="n">
+        <v>61</v>
+      </c>
       <c r="Q205" t="b">
         <v>0</v>
       </c>
@@ -13224,6 +15369,19 @@
           <t>NEINDP</t>
         </is>
       </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P206" t="n">
+        <v>62</v>
+      </c>
       <c r="Q206" t="b">
         <v>0</v>
       </c>
@@ -13286,6 +15444,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P207" t="n">
+        <v>36</v>
+      </c>
       <c r="Q207" t="b">
         <v>0</v>
       </c>
@@ -13348,6 +15519,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P208" t="n">
+        <v>64</v>
+      </c>
       <c r="Q208" t="b">
         <v>0</v>
       </c>
@@ -13472,6 +15656,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P210" t="n">
+        <v>40</v>
+      </c>
       <c r="Q210" t="b">
         <v>0</v>
       </c>
@@ -13534,6 +15731,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P211" t="n">
+        <v>47</v>
+      </c>
       <c r="Q211" t="b">
         <v>0</v>
       </c>
@@ -13596,6 +15806,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P212" t="n">
+        <v>40</v>
+      </c>
       <c r="Q212" t="b">
         <v>0</v>
       </c>
@@ -13658,6 +15881,19 @@
           <t>PDA</t>
         </is>
       </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P213" t="n">
+        <v>63</v>
+      </c>
       <c r="Q213" t="b">
         <v>0</v>
       </c>
@@ -13720,6 +15956,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P214" t="n">
+        <v>59</v>
+      </c>
       <c r="Q214" t="b">
         <v>0</v>
       </c>
@@ -13782,6 +16031,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P215" t="n">
+        <v>45</v>
+      </c>
       <c r="Q215" t="b">
         <v>0</v>
       </c>
@@ -13844,6 +16106,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P216" t="n">
+        <v>45</v>
+      </c>
       <c r="Q216" t="b">
         <v>0</v>
       </c>
@@ -13968,6 +16243,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P218" t="n">
+        <v>56</v>
+      </c>
       <c r="Q218" t="b">
         <v>1</v>
       </c>
@@ -14030,6 +16318,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P219" t="n">
+        <v>52</v>
+      </c>
       <c r="Q219" t="b">
         <v>0</v>
       </c>
@@ -14092,6 +16393,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P220" t="n">
+        <v>46</v>
+      </c>
       <c r="Q220" t="b">
         <v>0</v>
       </c>
@@ -14154,6 +16468,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P221" t="n">
+        <v>54</v>
+      </c>
       <c r="Q221" t="b">
         <v>0</v>
       </c>
@@ -14278,6 +16605,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P223" t="n">
+        <v>42</v>
+      </c>
       <c r="Q223" t="b">
         <v>0</v>
       </c>
@@ -14340,6 +16680,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P224" t="n">
+        <v>51</v>
+      </c>
       <c r="Q224" t="b">
         <v>0</v>
       </c>
@@ -14402,6 +16755,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P225" t="n">
+        <v>55</v>
+      </c>
       <c r="Q225" t="b">
         <v>1</v>
       </c>
@@ -14464,6 +16830,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P226" t="n">
+        <v>58</v>
+      </c>
       <c r="Q226" t="b">
         <v>0</v>
       </c>
@@ -14526,6 +16905,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P227" t="n">
+        <v>56</v>
+      </c>
       <c r="Q227" t="b">
         <v>0</v>
       </c>
@@ -14650,6 +17042,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P229" t="n">
+        <v>43</v>
+      </c>
       <c r="Q229" t="b">
         <v>0</v>
       </c>
@@ -14712,6 +17117,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P230" t="n">
+        <v>43</v>
+      </c>
       <c r="Q230" t="b">
         <v>0</v>
       </c>
@@ -14774,6 +17192,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P231" t="n">
+        <v>56</v>
+      </c>
       <c r="Q231" t="b">
         <v>1</v>
       </c>
@@ -14836,6 +17267,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P232" t="n">
+        <v>45</v>
+      </c>
       <c r="Q232" t="b">
         <v>0</v>
       </c>
@@ -14898,6 +17342,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P233" t="n">
+        <v>29</v>
+      </c>
       <c r="Q233" t="b">
         <v>0</v>
       </c>
@@ -15022,6 +17479,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P235" t="n">
+        <v>53</v>
+      </c>
       <c r="Q235" t="b">
         <v>0</v>
       </c>
@@ -15084,6 +17554,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P236" t="n">
+        <v>67</v>
+      </c>
       <c r="Q236" t="b">
         <v>0</v>
       </c>
@@ -15146,6 +17629,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P237" t="n">
+        <v>51</v>
+      </c>
       <c r="Q237" t="b">
         <v>0</v>
       </c>
@@ -15208,6 +17704,19 @@
           <t>NEINDP</t>
         </is>
       </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P238" t="n">
+        <v>70</v>
+      </c>
       <c r="Q238" t="b">
         <v>0</v>
       </c>
@@ -15332,6 +17841,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P240" t="n">
+        <v>71</v>
+      </c>
       <c r="Q240" t="b">
         <v>1</v>
       </c>
@@ -15394,6 +17916,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P241" t="n">
+        <v>76</v>
+      </c>
       <c r="Q241" t="b">
         <v>0</v>
       </c>
@@ -15456,6 +17991,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P242" t="n">
+        <v>49</v>
+      </c>
       <c r="Q242" t="b">
         <v>0</v>
       </c>
@@ -15518,6 +18066,19 @@
           <t>NEINDP</t>
         </is>
       </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P243" t="n">
+        <v>57</v>
+      </c>
       <c r="Q243" t="b">
         <v>0</v>
       </c>
@@ -15580,6 +18141,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P244" t="n">
+        <v>57</v>
+      </c>
       <c r="Q244" t="b">
         <v>0</v>
       </c>
@@ -15642,6 +18216,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P245" t="n">
+        <v>39</v>
+      </c>
       <c r="Q245" t="b">
         <v>0</v>
       </c>
@@ -15704,6 +18291,19 @@
           <t>RPI(A)</t>
         </is>
       </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P246" t="n">
+        <v>52</v>
+      </c>
       <c r="Q246" t="b">
         <v>0</v>
       </c>
@@ -15766,6 +18366,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P247" t="n">
+        <v>43</v>
+      </c>
       <c r="Q247" t="b">
         <v>0</v>
       </c>
@@ -15828,6 +18441,19 @@
           <t>MNDF</t>
         </is>
       </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P248" t="n">
+        <v>68</v>
+      </c>
       <c r="Q248" t="b">
         <v>0</v>
       </c>
@@ -15890,6 +18516,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P249" t="n">
+        <v>53</v>
+      </c>
       <c r="Q249" t="b">
         <v>0</v>
       </c>
@@ -16014,6 +18653,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P251" t="n">
+        <v>41</v>
+      </c>
       <c r="Q251" t="b">
         <v>0</v>
       </c>
@@ -16076,6 +18728,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P252" t="n">
+        <v>54</v>
+      </c>
       <c r="Q252" t="b">
         <v>0</v>
       </c>
@@ -16138,6 +18803,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P253" t="n">
+        <v>52</v>
+      </c>
       <c r="Q253" t="b">
         <v>0</v>
       </c>
@@ -16200,6 +18878,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P254" t="n">
+        <v>41</v>
+      </c>
       <c r="Q254" t="b">
         <v>0</v>
       </c>
@@ -16262,6 +18953,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P255" t="n">
+        <v>62</v>
+      </c>
       <c r="Q255" t="b">
         <v>0</v>
       </c>
@@ -16324,6 +19028,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P256" t="n">
+        <v>56</v>
+      </c>
       <c r="Q256" t="b">
         <v>1</v>
       </c>
@@ -16386,6 +19103,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P257" t="n">
+        <v>33</v>
+      </c>
       <c r="Q257" t="b">
         <v>0</v>
       </c>
@@ -16510,6 +19240,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P259" t="n">
+        <v>50</v>
+      </c>
       <c r="Q259" t="b">
         <v>0</v>
       </c>
@@ -16572,6 +19315,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P260" t="n">
+        <v>54</v>
+      </c>
       <c r="Q260" t="b">
         <v>0</v>
       </c>
@@ -16634,6 +19390,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P261" t="n">
+        <v>58</v>
+      </c>
       <c r="Q261" t="b">
         <v>0</v>
       </c>
@@ -16696,6 +19465,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P262" t="n">
+        <v>66</v>
+      </c>
       <c r="Q262" t="b">
         <v>0</v>
       </c>
@@ -16820,6 +19602,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P264" t="n">
+        <v>51</v>
+      </c>
       <c r="Q264" t="b">
         <v>0</v>
       </c>
@@ -16882,6 +19677,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P265" t="n">
+        <v>53</v>
+      </c>
       <c r="Q265" t="b">
         <v>0</v>
       </c>
@@ -16944,8 +19752,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P266" t="n">
+        <v>52</v>
+      </c>
       <c r="Q266" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R266" t="n">
         <v>29</v>
@@ -17006,6 +19827,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P267" t="n">
+        <v>50</v>
+      </c>
       <c r="Q267" t="b">
         <v>0</v>
       </c>
@@ -17068,6 +19902,19 @@
           <t>MNDF</t>
         </is>
       </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P268" t="n">
+        <v>49</v>
+      </c>
       <c r="Q268" t="b">
         <v>0</v>
       </c>
@@ -17130,6 +19977,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P269" t="n">
+        <v>62</v>
+      </c>
       <c r="Q269" t="b">
         <v>0</v>
       </c>
@@ -17254,6 +20114,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P271" t="n">
+        <v>47</v>
+      </c>
       <c r="Q271" t="b">
         <v>0</v>
       </c>
@@ -17316,6 +20189,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P272" t="n">
+        <v>45</v>
+      </c>
       <c r="Q272" t="b">
         <v>0</v>
       </c>
@@ -17378,6 +20264,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P273" t="n">
+        <v>52</v>
+      </c>
       <c r="Q273" t="b">
         <v>0</v>
       </c>
@@ -17502,6 +20401,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P275" t="n">
+        <v>35</v>
+      </c>
       <c r="Q275" t="b">
         <v>0</v>
       </c>
@@ -17564,6 +20476,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P276" t="n">
+        <v>68</v>
+      </c>
       <c r="Q276" t="b">
         <v>1</v>
       </c>
@@ -17626,6 +20551,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P277" t="n">
+        <v>62</v>
+      </c>
       <c r="Q277" t="b">
         <v>0</v>
       </c>
@@ -17688,6 +20626,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P278" t="n">
+        <v>59</v>
+      </c>
       <c r="Q278" t="b">
         <v>0</v>
       </c>
@@ -17812,6 +20763,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P280" t="n">
+        <v>49</v>
+      </c>
       <c r="Q280" t="b">
         <v>0</v>
       </c>
@@ -17874,6 +20838,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P281" t="n">
+        <v>50</v>
+      </c>
       <c r="Q281" t="b">
         <v>0</v>
       </c>
@@ -17936,6 +20913,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P282" t="n">
+        <v>43</v>
+      </c>
       <c r="Q282" t="b">
         <v>0</v>
       </c>
@@ -18060,6 +21050,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P284" t="n">
+        <v>50</v>
+      </c>
       <c r="Q284" t="b">
         <v>0</v>
       </c>
@@ -18122,6 +21125,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P285" t="n">
+        <v>39</v>
+      </c>
       <c r="Q285" t="b">
         <v>0</v>
       </c>
@@ -18184,6 +21200,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P286" t="n">
+        <v>68</v>
+      </c>
       <c r="Q286" t="b">
         <v>0</v>
       </c>
@@ -18308,6 +21337,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P288" t="n">
+        <v>66</v>
+      </c>
       <c r="Q288" t="b">
         <v>1</v>
       </c>
@@ -18370,6 +21412,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P289" t="n">
+        <v>41</v>
+      </c>
       <c r="Q289" t="b">
         <v>0</v>
       </c>
@@ -18432,6 +21487,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P290" t="n">
+        <v>41</v>
+      </c>
       <c r="Q290" t="b">
         <v>0</v>
       </c>
@@ -18494,6 +21562,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P291" t="n">
+        <v>34</v>
+      </c>
       <c r="Q291" t="b">
         <v>0</v>
       </c>
@@ -18618,8 +21699,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P293" t="n">
+        <v>61</v>
+      </c>
       <c r="Q293" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R293" t="n">
         <v>29</v>
@@ -18680,6 +21774,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P294" t="n">
+        <v>66</v>
+      </c>
       <c r="Q294" t="b">
         <v>0</v>
       </c>
@@ -18742,6 +21849,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P295" t="n">
+        <v>42</v>
+      </c>
       <c r="Q295" t="b">
         <v>0</v>
       </c>
@@ -18804,8 +21924,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P296" t="n">
+        <v>33</v>
+      </c>
       <c r="Q296" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R296" t="n">
         <v>29</v>
@@ -18866,6 +21999,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P297" t="n">
+        <v>59</v>
+      </c>
       <c r="Q297" t="b">
         <v>0</v>
       </c>
@@ -18990,6 +22136,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P299" t="n">
+        <v>53</v>
+      </c>
       <c r="Q299" t="b">
         <v>0</v>
       </c>
@@ -19052,6 +22211,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P300" t="n">
+        <v>55</v>
+      </c>
       <c r="Q300" t="b">
         <v>0</v>
       </c>
@@ -19114,6 +22286,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P301" t="n">
+        <v>61</v>
+      </c>
       <c r="Q301" t="b">
         <v>0</v>
       </c>
@@ -19176,6 +22361,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P302" t="n">
+        <v>64</v>
+      </c>
       <c r="Q302" t="b">
         <v>0</v>
       </c>
@@ -19238,6 +22436,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P303" t="n">
+        <v>32</v>
+      </c>
       <c r="Q303" t="b">
         <v>0</v>
       </c>
@@ -19362,6 +22573,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P305" t="n">
+        <v>61</v>
+      </c>
       <c r="Q305" t="b">
         <v>0</v>
       </c>
@@ -19424,8 +22648,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P306" t="n">
+        <v>60</v>
+      </c>
       <c r="Q306" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R306" t="n">
         <v>29</v>
@@ -19486,6 +22723,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P307" t="n">
+        <v>42</v>
+      </c>
       <c r="Q307" t="b">
         <v>0</v>
       </c>
@@ -19548,6 +22798,19 @@
           <t>MNDF</t>
         </is>
       </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P308" t="n">
+        <v>50</v>
+      </c>
       <c r="Q308" t="b">
         <v>0</v>
       </c>
@@ -19610,6 +22873,19 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P309" t="n">
+        <v>30</v>
+      </c>
       <c r="Q309" t="b">
         <v>0</v>
       </c>
@@ -19672,6 +22948,19 @@
           <t>AITC</t>
         </is>
       </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P310" t="n">
+        <v>68</v>
+      </c>
       <c r="Q310" t="b">
         <v>0</v>
       </c>
@@ -19796,6 +23085,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P312" t="n">
+        <v>56</v>
+      </c>
       <c r="Q312" t="b">
         <v>0</v>
       </c>
@@ -19858,6 +23160,19 @@
           <t>NPEP</t>
         </is>
       </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P313" t="n">
+        <v>71</v>
+      </c>
       <c r="Q313" t="b">
         <v>0</v>
       </c>
@@ -19920,6 +23235,19 @@
           <t>NEINDP</t>
         </is>
       </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P314" t="n">
+        <v>40</v>
+      </c>
       <c r="Q314" t="b">
         <v>0</v>
       </c>
@@ -19982,6 +23310,19 @@
           <t>RPI(A)</t>
         </is>
       </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P315" t="n">
+        <v>36</v>
+      </c>
       <c r="Q315" t="b">
         <v>0</v>
       </c>
@@ -20044,6 +23385,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P316" t="n">
+        <v>40</v>
+      </c>
       <c r="Q316" t="b">
         <v>0</v>
       </c>
@@ -20106,6 +23460,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P317" t="n">
+        <v>56</v>
+      </c>
       <c r="Q317" t="b">
         <v>0</v>
       </c>
@@ -20168,6 +23535,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P318" t="n">
+        <v>52</v>
+      </c>
       <c r="Q318" t="b">
         <v>0</v>
       </c>
@@ -20292,8 +23672,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P320" t="n">
+        <v>66</v>
+      </c>
       <c r="Q320" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R320" t="n">
         <v>29</v>
@@ -20354,6 +23747,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P321" t="n">
+        <v>44</v>
+      </c>
       <c r="Q321" t="b">
         <v>0</v>
       </c>
@@ -20416,6 +23822,19 @@
           <t>LJP</t>
         </is>
       </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P322" t="n">
+        <v>59</v>
+      </c>
       <c r="Q322" t="b">
         <v>0</v>
       </c>
@@ -20540,6 +23959,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P324" t="n">
+        <v>57</v>
+      </c>
       <c r="Q324" t="b">
         <v>1</v>
       </c>
@@ -20602,6 +24034,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P325" t="n">
+        <v>42</v>
+      </c>
       <c r="Q325" t="b">
         <v>0</v>
       </c>
@@ -20663,6 +24108,19 @@
         <is>
           <t>NPEP</t>
         </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P326" t="n">
+        <v>56</v>
       </c>
       <c r="Q326" t="b">
         <v>0</v>

--- a/static/data/exports/Retro_MN_AE_2017.xlsx
+++ b/static/data/exports/Retro_MN_AE_2017.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -658,7 +658,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -690,7 +690,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -870,7 +870,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -945,7 +945,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P58" t="n">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P61" t="n">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P74" t="n">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P75" t="n">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P82" t="n">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P85" t="n">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P86" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P88" t="n">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P89" t="n">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P90" t="n">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P93" t="n">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P95" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P96" t="n">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P97" t="n">
@@ -7549,7 +7549,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P99" t="n">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P103" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P116" t="n">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P117" t="n">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P118" t="n">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P119" t="n">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P120" t="n">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P123" t="n">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P125" t="n">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P126" t="n">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P131" t="n">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P133" t="n">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P134" t="n">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P135" t="n">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P137" t="n">
@@ -10445,7 +10445,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -10595,7 +10595,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -10732,7 +10732,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P142" t="n">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P145" t="n">
@@ -11094,7 +11094,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P147" t="n">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P148" t="n">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P149" t="n">
@@ -11319,7 +11319,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P152" t="n">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P154" t="n">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P155" t="n">
@@ -11818,7 +11818,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P157" t="n">
@@ -11893,7 +11893,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P158" t="n">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P159" t="n">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P160" t="n">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P161" t="n">
@@ -12255,7 +12255,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P163" t="n">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P164" t="n">
@@ -12405,7 +12405,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P165" t="n">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P166" t="n">
@@ -12555,7 +12555,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P167" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P168" t="n">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P170" t="n">
@@ -12842,7 +12842,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P171" t="n">
@@ -12917,7 +12917,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P172" t="n">
@@ -12992,7 +12992,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P173" t="n">
@@ -13129,7 +13129,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P175" t="n">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P176" t="n">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P177" t="n">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P178" t="n">
@@ -13429,7 +13429,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P179" t="n">
@@ -13504,7 +13504,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P180" t="n">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P182" t="n">
@@ -13716,7 +13716,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P183" t="n">
@@ -13853,7 +13853,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P185" t="n">
@@ -13928,7 +13928,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P186" t="n">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P187" t="n">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P188" t="n">
@@ -14153,7 +14153,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P189" t="n">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P190" t="n">
@@ -14365,7 +14365,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P192" t="n">
@@ -14440,7 +14440,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P193" t="n">
@@ -14515,7 +14515,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P194" t="n">
@@ -14590,7 +14590,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P195" t="n">
@@ -14727,7 +14727,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P197" t="n">
@@ -14802,7 +14802,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P198" t="n">
@@ -14939,7 +14939,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P200" t="n">
@@ -15014,7 +15014,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P201" t="n">
@@ -15151,7 +15151,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P203" t="n">
@@ -15226,7 +15226,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P204" t="n">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P205" t="n">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P206" t="n">
@@ -15451,7 +15451,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P207" t="n">
@@ -15526,7 +15526,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P208" t="n">
@@ -15663,7 +15663,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P210" t="n">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P211" t="n">
@@ -15813,7 +15813,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P212" t="n">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P213" t="n">
@@ -15963,7 +15963,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P214" t="n">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P215" t="n">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P216" t="n">
@@ -16250,7 +16250,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P218" t="n">
@@ -16325,7 +16325,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P219" t="n">
@@ -16400,7 +16400,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P220" t="n">
@@ -16475,7 +16475,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P221" t="n">
@@ -16612,7 +16612,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P223" t="n">
@@ -16687,7 +16687,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P224" t="n">
@@ -16762,7 +16762,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P225" t="n">
@@ -16837,7 +16837,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P226" t="n">
@@ -16912,7 +16912,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P227" t="n">
@@ -17049,7 +17049,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P229" t="n">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P230" t="n">
@@ -17199,7 +17199,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P231" t="n">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P232" t="n">
@@ -17349,7 +17349,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P233" t="n">
@@ -17486,7 +17486,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P235" t="n">
@@ -17561,7 +17561,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P236" t="n">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P237" t="n">
@@ -17711,7 +17711,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P238" t="n">
@@ -17848,7 +17848,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P240" t="n">
@@ -17923,7 +17923,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P241" t="n">
@@ -17998,7 +17998,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P242" t="n">
@@ -18073,7 +18073,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P243" t="n">
@@ -18148,7 +18148,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P244" t="n">
@@ -18223,7 +18223,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P245" t="n">
@@ -18298,7 +18298,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P246" t="n">
@@ -18373,7 +18373,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P247" t="n">
@@ -18448,7 +18448,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P248" t="n">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P249" t="n">
@@ -18660,7 +18660,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P251" t="n">
@@ -18735,7 +18735,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P252" t="n">
@@ -18810,7 +18810,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P253" t="n">
@@ -18885,7 +18885,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P254" t="n">
@@ -18960,7 +18960,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P255" t="n">
@@ -19035,7 +19035,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P256" t="n">
@@ -19110,7 +19110,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P257" t="n">
@@ -19247,7 +19247,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P259" t="n">
@@ -19322,7 +19322,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P260" t="n">
@@ -19397,7 +19397,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P261" t="n">
@@ -19472,7 +19472,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P262" t="n">
@@ -19609,7 +19609,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P264" t="n">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P265" t="n">
@@ -19759,7 +19759,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P266" t="n">
@@ -19834,7 +19834,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P267" t="n">
@@ -19909,7 +19909,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P268" t="n">
@@ -19984,7 +19984,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P269" t="n">
@@ -20121,7 +20121,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P271" t="n">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P272" t="n">
@@ -20271,7 +20271,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P273" t="n">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P275" t="n">
@@ -20483,7 +20483,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P276" t="n">
@@ -20558,7 +20558,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P277" t="n">
@@ -20633,7 +20633,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P278" t="n">
@@ -20770,7 +20770,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P280" t="n">
@@ -20845,7 +20845,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P281" t="n">
@@ -20920,7 +20920,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P282" t="n">
@@ -21057,7 +21057,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P284" t="n">
@@ -21132,7 +21132,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P285" t="n">
@@ -21207,7 +21207,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P286" t="n">
@@ -21344,7 +21344,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P288" t="n">
@@ -21419,7 +21419,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P289" t="n">
@@ -21494,7 +21494,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P290" t="n">
@@ -21569,7 +21569,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P291" t="n">
@@ -21706,7 +21706,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P293" t="n">
@@ -21781,7 +21781,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P294" t="n">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P295" t="n">
@@ -21931,7 +21931,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P296" t="n">
@@ -22006,7 +22006,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P297" t="n">
@@ -22143,7 +22143,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P299" t="n">
@@ -22218,7 +22218,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P300" t="n">
@@ -22293,7 +22293,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P301" t="n">
@@ -22368,7 +22368,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P302" t="n">
@@ -22443,7 +22443,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P303" t="n">
@@ -22580,7 +22580,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P305" t="n">
@@ -22655,7 +22655,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P306" t="n">
@@ -22730,7 +22730,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P307" t="n">
@@ -22805,7 +22805,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P308" t="n">
@@ -22880,7 +22880,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P309" t="n">
@@ -22955,7 +22955,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P310" t="n">
@@ -23092,7 +23092,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P312" t="n">
@@ -23167,7 +23167,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P313" t="n">
@@ -23242,7 +23242,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P314" t="n">
@@ -23317,7 +23317,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P315" t="n">
@@ -23392,7 +23392,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P316" t="n">
@@ -23467,7 +23467,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P317" t="n">
@@ -23542,7 +23542,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P318" t="n">
@@ -23679,7 +23679,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P320" t="n">
@@ -23754,7 +23754,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P321" t="n">
@@ -23829,7 +23829,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P322" t="n">
@@ -23966,7 +23966,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P324" t="n">
@@ -24041,7 +24041,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P325" t="n">
@@ -24116,7 +24116,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P326" t="n">
